--- a/RAWDATA/obs_data_corr_6100_5500.xlsx
+++ b/RAWDATA/obs_data_corr_6100_5500.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/a048908_unipi_it/Documents/R/CHRONOS/NEWCODE/RAWDATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{CF14AA21-64BF-4F44-BEE0-D5974977ADC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D20F5897-E614-45A0-B6C3-18F0B2672DA6}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{29FE0741-3550-4469-97EC-6B0784A1161B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8D50DE6-C3CC-4915-B753-91BDA40F50B2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2591AB75-0193-49A9-968E-8CA7C48823ED}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>Basi I</t>
   </si>
@@ -104,9 +104,6 @@
     <t>Grotta San Michele Arcangelo I</t>
   </si>
   <si>
-    <t>Pulo di Molfetta Fondo Azzolini</t>
-  </si>
-  <si>
     <t>Palata 1</t>
   </si>
   <si>
@@ -306,6 +303,15 @@
   </si>
   <si>
     <t>Impressa (Graffita)</t>
+  </si>
+  <si>
+    <t>Balsignano I</t>
+  </si>
+  <si>
+    <t>La Farigoule 2</t>
+  </si>
+  <si>
+    <t>Pulo di Molfetta Fondo Azzollini</t>
   </si>
 </sst>
 </file>
@@ -742,7 +748,7 @@
     <col min="14" max="14" width="11.1796875" style="2" customWidth="1"/>
     <col min="15" max="15" width="12" style="3" customWidth="1"/>
     <col min="16" max="16" width="33.54296875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="8.26953125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="8.1796875" style="3" customWidth="1"/>
     <col min="18" max="18" width="9" style="3" customWidth="1"/>
     <col min="19" max="19" width="11" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="8.81640625" style="3"/>
@@ -750,61 +756,61 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="N1" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="Q1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="12" x14ac:dyDescent="0.3">
@@ -836,7 +842,7 @@
         <v>215</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K2" s="3">
         <v>6930</v>
@@ -848,22 +854,13 @@
         <v>5813</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="12" x14ac:dyDescent="0.3">
@@ -895,34 +892,25 @@
         <v>26</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M3" s="10">
         <v>5810</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>1</v>
-      </c>
-      <c r="R3" s="3">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="12" x14ac:dyDescent="0.3">
@@ -954,7 +942,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K4" s="3">
         <v>6925</v>
@@ -966,13 +954,13 @@
         <v>5810</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q4" s="3">
         <v>1</v>
@@ -1013,25 +1001,25 @@
         <v>9</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M5" s="10">
         <v>5798</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q5" s="3">
         <v>1</v>
@@ -1072,25 +1060,25 @@
         <v>16</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M6" s="10">
         <v>5798</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q6" s="3">
         <v>0</v>
@@ -1131,25 +1119,25 @@
         <v>6</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M7" s="11">
         <v>5782</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="Q7" s="3">
         <v>0</v>
@@ -1163,7 +1151,7 @@
     </row>
     <row r="8" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="B8" s="4">
         <v>16.575779000000001</v>
@@ -1190,25 +1178,25 @@
         <v>8</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M8" s="3">
         <v>5697</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q8" s="3">
         <v>1</v>
@@ -1222,7 +1210,7 @@
     </row>
     <row r="9" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4">
         <v>17.619800000000001</v>
@@ -1249,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K9" s="3">
         <v>6870</v>
@@ -1261,13 +1249,13 @@
         <v>5761</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q9" s="3">
         <v>1</v>
@@ -1308,25 +1296,25 @@
         <v>1</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M10" s="10">
         <v>5759</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="12" x14ac:dyDescent="0.3">
@@ -1358,25 +1346,25 @@
         <v>7</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M11" s="3">
         <v>5753</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="P11" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="Q11" s="3">
         <v>1</v>
@@ -1417,25 +1405,25 @@
         <v>6</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M12" s="10">
         <v>5751</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="P12" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="Q12" s="3">
         <v>1</v>
@@ -1476,25 +1464,25 @@
         <v>8</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M13" s="10">
         <v>5736</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
@@ -1535,25 +1523,25 @@
         <v>31</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M14" s="10">
         <v>5716</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P14" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="P14" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="Q14" s="3">
         <v>1</v>
@@ -1567,7 +1555,7 @@
     </row>
     <row r="15" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="4">
         <v>13.7567</v>
@@ -1594,39 +1582,30 @@
         <v>39</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M15" s="3">
         <v>5716</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="P15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1</v>
-      </c>
-      <c r="R15" s="3">
-        <v>1</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="4">
         <v>16.262599999999999</v>
@@ -1653,7 +1632,7 @@
         <v>16</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K16" s="3">
         <v>6810</v>
@@ -1665,18 +1644,18 @@
         <v>5704</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P16" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="4">
         <v>8.3282799999999995</v>
@@ -1703,25 +1682,25 @@
         <v>35</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M17" s="10">
         <v>5700</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P17" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="P17" s="7" t="s">
-        <v>54</v>
       </c>
       <c r="Q17" s="3">
         <v>0</v>
@@ -1735,7 +1714,7 @@
     </row>
     <row r="18" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="4">
         <v>16.5336</v>
@@ -1762,25 +1741,25 @@
         <v>12</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M18" s="3">
         <v>5680</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="12" x14ac:dyDescent="0.3">
@@ -1812,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K19" s="3">
         <v>6710</v>
@@ -1824,18 +1803,18 @@
         <v>5630</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P19" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="4">
         <v>18.479800000000001</v>
@@ -1862,7 +1841,7 @@
         <v>4</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K20" s="3">
         <v>6622</v>
@@ -1874,13 +1853,13 @@
         <v>5623</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="12" x14ac:dyDescent="0.3">
@@ -1912,25 +1891,25 @@
         <v>8</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M21" s="10">
         <v>5522</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P21" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>54</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
@@ -1971,25 +1950,25 @@
         <v>5</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M22" s="10">
         <v>5585</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P22" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="P22" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="12" x14ac:dyDescent="0.3">
@@ -2021,25 +2000,25 @@
         <v>44</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M23" s="10">
         <v>5560</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q23" s="3">
         <v>1</v>
@@ -2064,41 +2043,41 @@
       <c r="D24" s="9">
         <v>42</v>
       </c>
-      <c r="E24" s="9">
-        <v>65</v>
-      </c>
-      <c r="F24" s="9">
-        <v>20</v>
-      </c>
-      <c r="G24" s="9">
-        <v>4</v>
-      </c>
-      <c r="H24" s="9">
-        <v>61</v>
+      <c r="E24" s="2">
+        <v>74</v>
+      </c>
+      <c r="F24" s="2">
+        <v>51</v>
+      </c>
+      <c r="G24" s="2">
+        <v>2</v>
+      </c>
+      <c r="H24" s="2">
+        <v>41</v>
       </c>
       <c r="I24" s="9">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M24" s="10">
         <v>5555</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O24" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P24" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="Q24" s="3">
         <v>1</v>
@@ -2139,25 +2118,25 @@
         <v>26</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M25" s="10">
         <v>5547</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="Q25" s="3">
         <v>0</v>
@@ -2183,10 +2162,10 @@
         <v>71</v>
       </c>
       <c r="E26" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" s="9">
         <v>0</v>
@@ -2198,30 +2177,39 @@
         <v>10</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M26" s="10">
         <v>5539</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>1</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" s="4">
         <v>16.0657</v>
@@ -2248,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K27" s="3">
         <v>6576</v>
@@ -2260,22 +2248,13 @@
         <v>5529</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>1</v>
-      </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="12" x14ac:dyDescent="0.3">
@@ -2295,7 +2274,7 @@
         <v>8</v>
       </c>
       <c r="F28" s="9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G28" s="9">
         <v>0</v>
@@ -2304,28 +2283,28 @@
         <v>0</v>
       </c>
       <c r="I28" s="9">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M28" s="10">
         <v>5518</v>
       </c>
-      <c r="N28" s="2" t="s">
-        <v>74</v>
+      <c r="N28" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="O28" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P28" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="P28" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="Q28" s="3">
         <v>1</v>
@@ -2366,25 +2345,25 @@
         <v>1</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M29" s="10">
         <v>5513.3050029501865</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="12" x14ac:dyDescent="0.3">
@@ -2416,25 +2395,25 @@
         <v>1060</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M30" s="10">
         <v>5676</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q30" s="3">
         <v>1</v>
@@ -2475,31 +2454,31 @@
         <v>7</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M31" s="10">
         <v>5500</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q31" s="3">
         <v>1</v>
       </c>
       <c r="R31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="3">
         <v>0</v>
@@ -2507,7 +2486,7 @@
     </row>
     <row r="32" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B32" s="4">
         <v>15.417999999999999</v>
@@ -2534,30 +2513,30 @@
         <v>1</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M32" s="3">
         <v>5485</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O32" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P32" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="P32" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B33" s="13">
         <v>8.9212659999999993</v>
@@ -2578,32 +2557,32 @@
         <v>0</v>
       </c>
       <c r="H33" s="9">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I33" s="9">
-        <v>653</v>
+        <v>607</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M33" s="3">
         <v>5572</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O33" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P33" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="P33" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="Q33" s="3">
         <v>0</v>
       </c>
@@ -2614,13 +2593,123 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
+    <row r="34" spans="1:19" ht="12" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="2">
+        <v>16.721499999999999</v>
+      </c>
+      <c r="C34" s="2">
+        <v>41.069600000000001</v>
+      </c>
+      <c r="D34" s="9">
+        <v>129</v>
+      </c>
+      <c r="E34" s="9">
+        <v>20</v>
+      </c>
+      <c r="F34" s="9">
+        <v>17</v>
+      </c>
+      <c r="G34" s="9">
+        <v>1</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="9">
+        <v>38</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M34" s="2">
+        <v>5529</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>1</v>
+      </c>
+      <c r="R34" s="3">
+        <v>1</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="12" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="2">
+        <v>4.3122199999999999</v>
+      </c>
+      <c r="C35" s="2">
+        <v>43.756900000000002</v>
+      </c>
+      <c r="D35" s="9">
+        <v>130</v>
+      </c>
+      <c r="E35" s="9">
+        <v>1</v>
+      </c>
+      <c r="F35" s="9">
+        <v>1</v>
+      </c>
+      <c r="G35" s="9">
+        <v>1</v>
+      </c>
+      <c r="H35" s="9">
+        <v>1</v>
+      </c>
+      <c r="I35" s="9">
+        <v>4</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M35" s="10">
+        <v>5500</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>0</v>
+      </c>
+      <c r="R35" s="4">
+        <v>1</v>
+      </c>
+      <c r="S35" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B36" s="4"/>
